--- a/artfynd/A 34468-2024 artfynd.xlsx
+++ b/artfynd/A 34468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,122 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120193175</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57260</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillahemsgölen, Lillahemsgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>511706</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6391562</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Uppvaktas intensivt av mesar sär den hoppar runt i en reslig gran</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bob Lind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bob Lind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34468-2024 artfynd.xlsx
+++ b/artfynd/A 34468-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119713157</v>
       </c>
       <c r="B2" t="n">
-        <v>91842</v>
+        <v>91860</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>120193175</v>
       </c>
       <c r="B3" t="n">
-        <v>57260</v>
+        <v>57270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34468-2024 artfynd.xlsx
+++ b/artfynd/A 34468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120528339</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillahemsgölen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>511576</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6391690</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eksjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johannes Glännman, Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
